--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/TEXAS_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/TEXAS_2020.xlsx
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C137">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Praxedis G. Guerero</t>
+          <t>Praxedis G. Guerrero</t>
         </is>
       </c>
       <c r="C159">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C179">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C184">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C244">
@@ -5017,7 +5017,7 @@
         <v>95</v>
       </c>
       <c r="D259">
-        <v>0.0009201592359772575</v>
+        <v>0.0009201592359772576</v>
       </c>
     </row>
     <row r="260">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C275">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C346">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C381">
@@ -7375,7 +7375,7 @@
         <v>99</v>
       </c>
       <c r="D390">
-        <v>0.0009589027827552473</v>
+        <v>0.0009589027827552472</v>
       </c>
     </row>
     <row r="391">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C392">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C402">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C498">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C562">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C568">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C692">
@@ -14863,7 +14863,7 @@
         <v>98</v>
       </c>
       <c r="D806">
-        <v>0.0009492168960607499</v>
+        <v>0.00094921689606075</v>
       </c>
     </row>
     <row r="807">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C878">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C880">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C881">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>Cuilapam De Guerero</t>
+          <t>Cuilapam De Guerrero</t>
         </is>
       </c>
       <c r="C922">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C944">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1015">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1016">
@@ -18744,7 +18744,7 @@
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1022">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C1156">
@@ -21948,7 +21948,7 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C1200">
@@ -23478,7 +23478,7 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Totoltepec De Guerero</t>
+          <t>Totoltepec De Guerrero</t>
         </is>
       </c>
       <c r="C1285">
@@ -23568,7 +23568,7 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C1290">
@@ -24025,7 +24025,7 @@
         <v>94</v>
       </c>
       <c r="D1315">
-        <v>0.0009104733492827601</v>
+        <v>0.00091047334928276</v>
       </c>
     </row>
     <row r="1316">
@@ -26664,7 +26664,7 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C1462">
@@ -27222,7 +27222,7 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Amaxac De Guerero</t>
+          <t>Amaxac De Guerrero</t>
         </is>
       </c>
       <c r="C1493">
@@ -28669,7 +28669,7 @@
         <v>94</v>
       </c>
       <c r="D1573">
-        <v>0.0009104733492827601</v>
+        <v>0.00091047334928276</v>
       </c>
     </row>
     <row r="1574">
@@ -31117,7 +31117,7 @@
         <v>99</v>
       </c>
       <c r="D1709">
-        <v>0.0009589027827552473</v>
+        <v>0.0009589027827552472</v>
       </c>
     </row>
     <row r="1710">
